--- a/public/route-rationalization-kashmir/Kashmir_Route_Verification_Appendix_v3.4.4_RTO.xlsx
+++ b/public/route-rationalization-kashmir/Kashmir_Route_Verification_Appendix_v3.4.4_RTO.xlsx
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Independent real-world verification of all 186 active routes; 48 distance corrections applied. Prepared 2026-06-25.</t>
+          <t>Independent real-world verification of all 186 active routes; 49 distance corrections applied. Prepared 2026-06-25.</t>
         </is>
       </c>
     </row>
@@ -614,11 +614,11 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>42 over-modelled shrank, 6 under-modelled grew</t>
+          <t>inc. 4 re-geocoded+re-routed; 43 shrank, 6 grew</t>
         </is>
       </c>
     </row>
@@ -630,12 +630,12 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Srinagar-Budgam, GBS-Lal Chowk (geometry redrawn)</t>
+          <t>Budgam, GBS, Hazratbal, Manigam (geometry redrawn)</t>
         </is>
       </c>
     </row>
@@ -646,11 +646,11 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>12 SSCL via-loop, 19 name-unverifiable, 14 within tolerance</t>
+          <t>11 SSCL via-loop, 19 name-unverifiable, 14 within tolerance</t>
         </is>
       </c>
     </row>
@@ -749,7 +749,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K49"/>
+  <dimension ref="A1:K50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -882,37 +882,37 @@
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>SRSR02021523</t>
+          <t>SRGB02020503</t>
         </is>
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>GBS to LAL Chowk</t>
+          <t>Batamaloo to Manigam</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>Peri_Urban</t>
+          <t>Regional_District</t>
         </is>
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>20.33</t>
+          <t>54.47</t>
         </is>
       </c>
       <c r="E3" s="7" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>37.09</t>
         </is>
       </c>
       <c r="F3" s="6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>13</t>
         </is>
       </c>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H3" s="6" t="inlineStr">
@@ -922,49 +922,49 @@
       </c>
       <c r="I3" s="6" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J3" s="6" t="inlineStr">
         <is>
-          <t>Origin re-geocoded to General Bus Stand Batamaloo; OSRM-rerouted to Lal Chowk = 2.93 km (was 20.3 km spurious). Geometry + numbers corrected.</t>
+          <t>SSCL trunk. Blind audit found the destination pin ~15 km too far east; re-geocoded to real Manigam (Lar, Ganderbal 34.282,74.800), OSRM-rerouted = 37.1 km (was 54.5). Geometry + distance corrected; SSCL fleet kept at the empirical 13.</t>
         </is>
       </c>
       <c r="K3" s="6" t="inlineStr">
         <is>
-          <t>onefivenine.com,kashmirlife.net,manual haversine calculation</t>
+          <t>blind re-verification; onefivenine.com Manigam; distancebetween2.com Srinagar-Ganderbal</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>SRSR02023736</t>
+          <t>SRSR02021523</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>Safakadal to SMHS</t>
+          <t>GBS to LAL Chowk</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Urban</t>
+          <t>Peri_Urban</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>6.26</t>
+          <t>20.33</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -984,54 +984,54 @@
       </c>
       <c r="J4" s="6" t="inlineStr">
         <is>
-          <t>Safakadal-SMHS is ~0.8-1.6 km (engine 6.26 km stale); set to verified ~1.5 km.</t>
+          <t>Origin re-geocoded to General Bus Stand Batamaloo; OSRM-rerouted to Lal Chowk = 2.93 km (was 20.3 km spurious). Geometry + numbers corrected.</t>
         </is>
       </c>
       <c r="K4" s="6" t="inlineStr">
         <is>
-          <t>onefivenine.com,jkb.bank.in,justdial.com</t>
+          <t>onefivenine.com,kashmirlife.net,manual haversine calculation</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>ANSP01010106</t>
+          <t>SRSR02022941</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>Anantnagh to Shopian</t>
+          <t>Hazratbal, Lalbazar</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>Regional_District</t>
+          <t>Urban</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>43.84</t>
+          <t>8.81</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>6.36</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="I5" s="6" t="inlineStr">
@@ -1041,54 +1041,54 @@
       </c>
       <c r="J5" s="6" t="inlineStr">
         <is>
-          <t>Real driving distance is ~34 km direct (distancebetween2) up to ~40 km via Zainapora; engine 43.8 km is ~18% high. Recommend trimming Route_KM toward ~37-40 km.</t>
+          <t>Origin re-geocoded to the real Hazratbal shrine (34.127,74.836) after the independent blind audit flagged the pin at Parimpora; OSRM-rerouted to Lal Bazar = 6.36 km. Geometry redrawn.</t>
         </is>
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>distancebetween2.com, distancesfrom.com, jksrtc.co.in</t>
+          <t>onefivenine.com (Lal Bazar); wikipedia.org (Hazratbal); indiainfo.net</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>BGSR02020820</t>
+          <t>SRSR02023736</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>Narbal to Jehangir Chowk</t>
+          <t>Safakadal to SMHS</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Peri_Urban</t>
+          <t>Urban</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>21.63</t>
+          <t>6.26</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="I6" s="6" t="inlineStr">
@@ -1098,24 +1098,24 @@
       </c>
       <c r="J6" s="6" t="inlineStr">
         <is>
-          <t>Corridor strongly verified as real and currently operated (existing Bus Route 10 Narbal Crossing-Pantha Chowk documented on tellmyroute with 21 stops); sources put Narbal at roughly 16-18km from Srinagar via the Gulmarg road, somewhat under the engine's 21.6km, and the modelled one-way time of ~54 min looks too slow for this stretch.</t>
+          <t>Safakadal-SMHS is ~0.8-1.6 km (engine 6.26 km stale); set to verified ~1.5 km.</t>
         </is>
       </c>
       <c r="K6" s="6" t="inlineStr">
         <is>
-          <t>tellmyroute.com, distancesfrom.com, prokerala.com</t>
+          <t>onefivenine.com,jkb.bank.in,justdial.com</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>BRSR05020139</t>
+          <t>ANSP01010106</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>Zaloora to Srinagar</t>
+          <t>Anantnagh to Shopian</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>63.13</t>
+          <t>43.84</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>37.0</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
@@ -1150,54 +1150,54 @@
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>Zaloora is a village in the Zaingair belt of Sopore division. Srinagar-Sopore ~49 km by road; Zaloora a few km off (~50-55 km). Modelled 63.1 km is ~21% high - likely a via-routing detour. Corridor real and well-served. Fix: verify routing does not loop via Baramulla.</t>
+          <t>Real driving distance is ~34 km direct (distancebetween2) up to ~40 km via Zainapora; engine 43.8 km is ~18% high. Recommend trimming Route_KM toward ~37-40 km.</t>
         </is>
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>en.wikipedia.org/wiki/Sopore; distancebetween2.com sopore/srinagar (49 km); distancesfrom.com</t>
+          <t>distancebetween2.com, distancesfrom.com, jksrtc.co.in</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>KWSR03020339</t>
+          <t>BGSR02020820</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>Kupwara to Srinagar</t>
+          <t>Narbal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Regional_District</t>
+          <t>Peri_Urban</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>102.96</t>
+          <t>21.63</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
@@ -1207,54 +1207,54 @@
       </c>
       <c r="I8" s="6" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>Real Kupwara-Srinagar driving distance is ~86.7km (tourtravelworld/distancebetween2); engine 103km is +19% over. Likely routes via a longer Handwara/Sopore detour rather than the direct line. Corridor and service real (SRTC runs it). Recommend trimming Route_KM toward ~88-90km; fleet of 9 then eases.</t>
+          <t>Corridor strongly verified as real and currently operated (existing Bus Route 10 Narbal Crossing-Pantha Chowk documented on tellmyroute with 21 stops); sources put Narbal at roughly 16-18km from Srinagar via the Gulmarg road, somewhat under the engine's 21.6km, and the modelled one-way time of ~54 min looks too slow for this stretch.</t>
         </is>
       </c>
       <c r="K8" s="6" t="inlineStr">
         <is>
-          <t>tourtravelworld.com srinagar-to-kupwara, distancebetween2.com/srinagar/kupwara, kupwara.nic.in, jksrtc.co.in</t>
+          <t>tellmyroute.com, distancesfrom.com, prokerala.com</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>PWSR03020239</t>
+          <t>BRSR05020139</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>Koil to Srinagar</t>
+          <t>Zaloora to Srinagar</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Peri_Urban</t>
+          <t>Regional_District</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>32.73</t>
+          <t>63.13</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
@@ -1264,29 +1264,29 @@
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>Real, well-documented village (Koil, approx 28km from Srinagar per village records) with the model's 32.7km running about 17% above the cited figure - just outside a tight PASS band but a minor, plausible delta likely reflecting actual road routing versus the village record's more direct figure. Headway/fleet (35 min/6 buses) reasonable for a rural lifeline.</t>
+          <t>Zaloora is a village in the Zaingair belt of Sopore division. Srinagar-Sopore ~49 km by road; Zaloora a few km off (~50-55 km). Modelled 63.1 km is ~21% high - likely a via-routing detour. Corridor real and well-served. Fix: verify routing does not loop via Baramulla.</t>
         </is>
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>onefivenine.com,jkpanchayat.jk.gov.in,soki.in</t>
+          <t>en.wikipedia.org/wiki/Sopore; distancebetween2.com sopore/srinagar (49 km); distancesfrom.com</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>SPSR01020539</t>
+          <t>KWSR03020339</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>Sedow to Srinagar</t>
+          <t>Kupwara to Srinagar</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
@@ -1296,22 +1296,22 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>57.77</t>
+          <t>102.96</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
@@ -1326,49 +1326,49 @@
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>Sedow is officially 46 km from Srinagar (shopian.nic.in / icbse); engine models 57.8 km (+26%). Endpoint correct but distance over-modelled - recommend re-check OSRM path, target ~46-50 km.</t>
+          <t>Real Kupwara-Srinagar driving distance is ~86.7km (tourtravelworld/distancebetween2); engine 103km is +19% over. Likely routes via a longer Handwara/Sopore detour rather than the direct line. Corridor and service real (SRTC runs it). Recommend trimming Route_KM toward ~88-90km; fleet of 9 then eases.</t>
         </is>
       </c>
       <c r="K10" s="6" t="inlineStr">
         <is>
-          <t>shopian.nic.in, geolysis.com, icbse.com</t>
+          <t>tourtravelworld.com srinagar-to-kupwara, distancebetween2.com/srinagar/kupwara, kupwara.nic.in, jksrtc.co.in</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>SRBG02013902</t>
+          <t>PWSR03020239</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>Srinagar to Beeru</t>
+          <t>Koil to Srinagar</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Regional_District</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="inlineStr">
-        <is>
-          <t>15.28</t>
-        </is>
-      </c>
-      <c r="E11" s="8" t="inlineStr">
-        <is>
-          <t>25.0</t>
+          <t>Peri_Urban</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>32.73</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>17.5</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
@@ -1378,44 +1378,44 @@
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>Raiyar (Beeru) in Khan-Sahib block is ~25 km from Srinagar by road; engine coord (34.014,74.719) sits only 11.5 km straight-line, pinned too close to Srinagar (real Beeru ~33.96N,74.65E). Engine 15.3 km under-models by ~39%. Re-pin endpoint and re-route.</t>
+          <t>Real, well-documented village (Koil, approx 28km from Srinagar per village records) with the model's 32.7km running about 17% above the cited figure - just outside a tight PASS band but a minor, plausible delta likely reflecting actual road routing versus the village record's more direct figure. Headway/fleet (35 min/6 buses) reasonable for a rural lifeline.</t>
         </is>
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>onefivenine.com/Raiyar-Beeru/Khan-sahib; villageinfo.in raiyar-beruwa; budgam.nic.in Doodhpathri</t>
+          <t>onefivenine.com,jkpanchayat.jk.gov.in,soki.in</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>SRBG02014001</t>
+          <t>SPSR01020539</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>TRC Srinagar to Airport</t>
+          <t>Sedow to Srinagar</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Urban</t>
+          <t>Regional_District</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>14.52</t>
+          <t>57.77</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
@@ -1435,29 +1435,29 @@
       </c>
       <c r="I12" s="6" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>Real, well known TRC-to-Airport corridor with both endpoints correctly placed; however multiple sources converge on roughly 12 km while the engine models 14.5 km (about 21% over), and the modelled one-way time of ~58 min is long for this corridor versus the commonly cited 20-30 min airport transfer time -- worth rechecking the routed path for unnecessary detour.</t>
+          <t>Sedow is officially 46 km from Srinagar (shopian.nic.in / icbse); engine models 57.8 km (+26%). Endpoint correct but distance over-modelled - recommend re-check OSRM path, target ~46-50 km.</t>
         </is>
       </c>
       <c r="K12" s="6" t="inlineStr">
         <is>
-          <t>distancesfrom.com, distcalculator.com, clearcarrental.com</t>
+          <t>shopian.nic.in, geolysis.com, icbse.com</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>SRBG02022003</t>
+          <t>SRBG02013902</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>Jehangir Chowk to Budgam</t>
+          <t>Srinagar to Beeru</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -1465,24 +1465,24 @@
           <t>Regional_District</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>45.58</t>
-        </is>
-      </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>11.5</t>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>15.28</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>25.0</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
@@ -1497,39 +1497,39 @@
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>Straight-line is only 16.7km but engine road=45.6km (circuity 2.73x); real Srinagar/Jehangir Chowk to Budgam is ~10-13km by road. Engine over-modeled the corridor ~4x - likely a routing detour artifact. Fix Route_KM to ~11-13km; cycle/fleet should drop accordingly.</t>
+          <t>Raiyar (Beeru) in Khan-Sahib block is ~25 km from Srinagar by road; engine coord (34.014,74.719) sits only 11.5 km straight-line, pinned too close to Srinagar (real Beeru ~33.96N,74.65E). Engine 15.3 km under-models by ~39%. Re-pin endpoint and re-route.</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>yatra.com budgam-to-srinagar (9km), mapsofindia.com budgam-to-srinagar, haversine 16.7km</t>
+          <t>onefivenine.com/Raiyar-Beeru/Khan-sahib; villageinfo.in raiyar-beruwa; budgam.nic.in Doodhpathri</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>SRBG02022203</t>
+          <t>SRBG02014001</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>LD to Budgam</t>
+          <t>TRC Srinagar to Airport</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Peri_Urban</t>
+          <t>Urban</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>21.78</t>
+          <t>14.52</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
@@ -1554,49 +1554,49 @@
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>Multiple independent sources (Yatra, ClearCarRental, MapsOfIndia) converge on Srinagar-Budgam direct road distance of 9-14km, well under the engine's 21.8km; even allowing for LD not being the literal city centre, the modelled distance looks ~50-60% too long for a direct LD-Budgam corridor unless routed via a long detour.</t>
+          <t>Real, well known TRC-to-Airport corridor with both endpoints correctly placed; however multiple sources converge on roughly 12 km while the engine models 14.5 km (about 21% over), and the modelled one-way time of ~58 min is long for this corridor versus the commonly cited 20-30 min airport transfer time -- worth rechecking the routed path for unnecessary detour.</t>
         </is>
       </c>
       <c r="K14" s="6" t="inlineStr">
         <is>
-          <t>yatra.com, clearcarrental.com, mapsofindia.com</t>
+          <t>distancesfrom.com, distcalculator.com, clearcarrental.com</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>SRBG02022903</t>
+          <t>SRBG02022003</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>Parimpora to Budgam</t>
+          <t>Jehangir Chowk to Budgam</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>Peri_Urban</t>
+          <t>Regional_District</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>31.39</t>
+          <t>45.58</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>11.5</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H15" s="6" t="inlineStr">
@@ -1606,56 +1606,56 @@
       </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>Multiple sources converge on a 9-21km Srinagar/Parimpora-Budgam road distance (yatra.com 9-10km; citymeter.net/distancesfrom.com 13-21km), but the engine models this leg at 31.4km, well above that band; this looks like the engine routing a longer detour than the real shortest road path between these two points, the largest distance discrepancy found in this batch and worth an engineering check even though both endpoints individually are correctly placed.</t>
+          <t>Straight-line is only 16.7km but engine road=45.6km (circuity 2.73x); real Srinagar/Jehangir Chowk to Budgam is ~10-13km by road. Engine over-modeled the corridor ~4x - likely a routing detour artifact. Fix Route_KM to ~11-13km; cycle/fleet should drop accordingly.</t>
         </is>
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>yatra.com, citymeter.net, distancesfrom.com, mapsofindia.com</t>
+          <t>yatra.com budgam-to-srinagar (9km), mapsofindia.com budgam-to-srinagar, haversine 16.7km</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>SRBG02023902</t>
+          <t>SRBG02022203</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>Srinagar to Badrun</t>
+          <t>LD to Budgam</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Regional_District</t>
+          <t>Peri_Urban</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>33.31</t>
+          <t>21.78</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G16" s="6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
           <t>AUTO</t>
@@ -1663,54 +1663,54 @@
       </c>
       <c r="I16" s="6" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J16" s="6" t="inlineStr">
         <is>
-          <t>Badran/Budran is a village in Beerwah/Magam tehsil ~25 km from Srinagar; engine 33.3 km is ~33% high (likely a via-routing/coord overshoot west). Corridor real and served. Suggest trimming Route_KM toward ~25 km.</t>
+          <t>Multiple independent sources (Yatra, ClearCarRental, MapsOfIndia) converge on Srinagar-Budgam direct road distance of 9-14km, well under the engine's 21.8km; even allowing for LD not being the literal city centre, the modelled distance looks ~50-60% too long for a direct LD-Budgam corridor unless routed via a long detour.</t>
         </is>
       </c>
       <c r="K16" s="6" t="inlineStr">
         <is>
-          <t>onefivenine.com (Budran/Khag); en.wikipedia.org/wiki/Badran,_Kashmir; en.wikipedia.org/wiki/Beerwah</t>
+          <t>yatra.com, clearcarrental.com, mapsofindia.com</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>SRBG02023904</t>
+          <t>SRBG02022903</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Srinagar to Chewdara</t>
+          <t>Parimpora to Budgam</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>Regional_District</t>
+          <t>Peri_Urban</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>28.16</t>
+          <t>31.39</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H17" s="6" t="inlineStr">
@@ -1720,29 +1720,29 @@
       </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t>Chewdara (Beerwah block) is ~23 km from Srinagar (3 km from Beerwah). Engine 28.2 km is ~22% high. Real corridor and service exist; trim Route_KM toward ~23 km.</t>
+          <t>Multiple sources converge on a 9-21km Srinagar/Parimpora-Budgam road distance (yatra.com 9-10km; citymeter.net/distancesfrom.com 13-21km), but the engine models this leg at 31.4km, well above that band; this looks like the engine routing a longer detour than the real shortest road path between these two points, the largest distance discrepancy found in this batch and worth an engineering check even though both endpoints individually are correctly placed.</t>
         </is>
       </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
-          <t>onefivenine.com Chewdara-A/Beerwah; en.wikipedia.org/wiki/Chewdara; indiainfo.net pincode 193411</t>
+          <t>yatra.com, citymeter.net, distancesfrom.com, mapsofindia.com</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>SRBG02023905</t>
+          <t>SRBG02023902</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Srinagar to Isganderpora</t>
+          <t>Srinagar to Badrun</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
@@ -1752,17 +1752,17 @@
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>33.62</t>
+          <t>33.31</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>26.5</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G18" s="6" t="inlineStr">
@@ -1782,24 +1782,24 @@
       </c>
       <c r="J18" s="6" t="inlineStr">
         <is>
-          <t>Iskanderpora (Beerwah block, pincode 193411 with Beerwah/Chewdara/Kandoora) sits in the ~25-28 km belt; engine 33.6 km is ~27% high (via-routing overshoot). Real corridor; trim Route_KM.</t>
+          <t>Badran/Budran is a village in Beerwah/Magam tehsil ~25 km from Srinagar; engine 33.3 km is ~33% high (likely a via-routing/coord overshoot west). Corridor real and served. Suggest trimming Route_KM toward ~25 km.</t>
         </is>
       </c>
       <c r="K18" s="6" t="inlineStr">
         <is>
-          <t>indiainfo.net pincode 193411 (Kandoora cluster); onefivenine.com Beerwah villages; en.wikipedia.org/wiki/Beerwah</t>
+          <t>onefivenine.com (Budran/Khag); en.wikipedia.org/wiki/Badran,_Kashmir; en.wikipedia.org/wiki/Beerwah</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>SRBG02023911</t>
+          <t>SRBG02023904</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Srinagar to Shanglipora</t>
+          <t>Srinagar to Chewdara</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
@@ -1809,22 +1809,22 @@
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>42.04</t>
+          <t>28.16</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H19" s="6" t="inlineStr">
@@ -1839,49 +1839,49 @@
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>Shanglipora is a village near Beerwah/Khansahib (W Budgam); Beerwah is 27-35 km by road, Shanglipora a few km further (~33-38 km). Modelled 42 km is ~20% high, likely a via-routing detour. Corridor real, headway sane. Fix: verify routing does not loop.</t>
+          <t>Chewdara (Beerwah block) is ~23 km from Srinagar (3 km from Beerwah). Engine 28.2 km is ~22% high. Real corridor and service exist; trim Route_KM toward ~23 km.</t>
         </is>
       </c>
       <c r="K19" s="6" t="inlineStr">
         <is>
-          <t>wikipedia.org/wiki/Beerwah; citymeter.net; onefivenine.com</t>
+          <t>onefivenine.com Chewdara-A/Beerwah; en.wikipedia.org/wiki/Chewdara; indiainfo.net pincode 193411</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>SRBG02032901</t>
+          <t>SRBG02023905</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>Parimpora to Chadora</t>
+          <t>Srinagar to Isganderpora</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Peri_Urban</t>
+          <t>Regional_District</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>25.75</t>
+          <t>33.62</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>26.5</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
@@ -1891,54 +1891,54 @@
       </c>
       <c r="I20" s="6" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J20" s="6" t="inlineStr">
         <is>
-          <t>Corridor independently corroborated (sources confirm shared sumo/bus services run from Chadoora/Charar-e-Sharief to Srinagar's Parimpora, Batamaloo or Lal Chowk stands), and Srinagar-Chadoora is documented at 14km by some sources though up to 22km by others including the connector road; engine's 25.75km runs on the high side of this range (roughly 17-84% over depending on the reference figure used) - flagged for a routing recheck similar to the Budgam-bound routes above, though less severe.</t>
+          <t>Iskanderpora (Beerwah block, pincode 193411 with Beerwah/Chewdara/Kandoora) sits in the ~25-28 km belt; engine 33.6 km is ~27% high (via-routing overshoot). Real corridor; trim Route_KM.</t>
         </is>
       </c>
       <c r="K20" s="6" t="inlineStr">
         <is>
-          <t>alldistancebetween.com, distancesfrom.com, etourismkashmir.com</t>
+          <t>indiainfo.net pincode 193411 (Kandoora cluster); onefivenine.com Beerwah villages; en.wikipedia.org/wiki/Beerwah</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>SRBG02033901</t>
+          <t>SRBG02023911</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>Srinagar to Chadoora</t>
+          <t>Srinagar to Shanglipora</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>Urban</t>
+          <t>Regional_District</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>16.89</t>
+          <t>42.04</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>14.5</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H21" s="6" t="inlineStr">
@@ -1948,54 +1948,54 @@
       </c>
       <c r="I21" s="6" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>Chadoora is consistently cited as 14-15 km from Srinagar (alldistancebetween.com, Wikipedia) versus the modelled 16.895 km, about a 17% overstatement at the edge of acceptable tolerance, and the one-way time of ~68 min is roughly 3x the realistic 20-25 min drive even accounting for the documented narrow/congested road locals want widened. Corridor is real and well-used; headway 35 min and fleet 5 are plausible for a peri-urban feeder of this length.</t>
+          <t>Shanglipora is a village near Beerwah/Khansahib (W Budgam); Beerwah is 27-35 km by road, Shanglipora a few km further (~33-38 km). Modelled 42 km is ~20% high, likely a via-routing detour. Corridor real, headway sane. Fix: verify routing does not loop.</t>
         </is>
       </c>
       <c r="K21" s="6" t="inlineStr">
         <is>
-          <t>alldistancebetween.com Srinagar-Chadoora, Wikipedia Chadoora, facebook.com Dr Raja Muzaffar Bhat 4-lane road petition</t>
+          <t>wikipedia.org/wiki/Beerwah; citymeter.net; onefivenine.com</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>SRBR02023902</t>
+          <t>SRBG02032901</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>Srinagar to URI Baramulla</t>
+          <t>Parimpora to Chadora</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Regional_District</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <t>77.62</t>
-        </is>
-      </c>
-      <c r="E22" s="8" t="inlineStr">
-        <is>
-          <t>101.0</t>
+          <t>Peri_Urban</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>25.75</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>18.0</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
@@ -2005,29 +2005,29 @@
       </c>
       <c r="I22" s="6" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J22" s="6" t="inlineStr">
         <is>
-          <t>Uri via Baramulla on NH1 is ~100-102 km by road (distancesfrom 102 km) vs modelled 77.6 km - ~24% under. Engine likely under-routed the Baramulla-Uri mountain leg. Coords good. Corridor real, well-served to Baramulla, thinner Baramulla-Uri (border/army area). Fix: correct road km to ~100 km, refleet/headway.</t>
+          <t>Corridor independently corroborated (sources confirm shared sumo/bus services run from Chadoora/Charar-e-Sharief to Srinagar's Parimpora, Batamaloo or Lal Chowk stands), and Srinagar-Chadoora is documented at 14km by some sources though up to 22km by others including the connector road; engine's 25.75km runs on the high side of this range (roughly 17-84% over depending on the reference figure used) - flagged for a routing recheck similar to the Budgam-bound routes above, though less severe.</t>
         </is>
       </c>
       <c r="K22" s="6" t="inlineStr">
         <is>
-          <t>en.wikipedia.org/wiki/Srinagar-Baramulla_highway; distancesfrom.com srinagar-to-Uri (102 km); nativeplanet.com</t>
+          <t>alldistancebetween.com, distancesfrom.com, etourismkashmir.com</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>SRGB01010903</t>
+          <t>SRBG02033901</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>Soura to Ganderbal</t>
+          <t>Srinagar to Chadoora</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
@@ -2035,24 +2035,24 @@
           <t>Urban</t>
         </is>
       </c>
-      <c r="D23" s="8" t="inlineStr">
-        <is>
-          <t>9.86</t>
-        </is>
-      </c>
-      <c r="E23" s="8" t="inlineStr">
-        <is>
-          <t>12.5</t>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>16.89</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>14.5</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H23" s="6" t="inlineStr">
@@ -2067,24 +2067,24 @@
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>Real driving distance for Soura/Srinagar to Ganderbal is commonly cited as 10-15 km depending on source and exact start point; modelled 9.86 km falls at the low end of that range, so it is plausible but on the short side. Treat as REVIEW for verification of the exact alignment used, not a hard error.</t>
+          <t>Chadoora is consistently cited as 14-15 km from Srinagar (alldistancebetween.com, Wikipedia) versus the modelled 16.895 km, about a 17% overstatement at the edge of acceptable tolerance, and the one-way time of ~68 min is roughly 3x the realistic 20-25 min drive even accounting for the documented narrow/congested road locals want widened. Corridor is real and well-used; headway 35 min and fleet 5 are plausible for a peri-urban feeder of this length.</t>
         </is>
       </c>
       <c r="K23" s="6" t="inlineStr">
         <is>
-          <t>distancebetween2.com, onefivenine.com, ganderbal.nic.in</t>
+          <t>alldistancebetween.com Srinagar-Chadoora, Wikipedia Chadoora, facebook.com Dr Raja Muzaffar Bhat 4-lane road petition</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>SRKW02013901</t>
+          <t>SRBR02023902</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>Srinagar to Chowkibal</t>
+          <t>Srinagar to URI Baramulla</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
@@ -2094,22 +2094,22 @@
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>94.97</t>
+          <t>77.62</t>
         </is>
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H24" s="6" t="inlineStr">
@@ -2124,49 +2124,49 @@
       </c>
       <c r="J24" s="6" t="inlineStr">
         <is>
-          <t>Chowkibal (Kupwara, on the Tangdhar/Sadhna Pass approach) real road ~125 km; engine 94.97 km under-models by ~25% - routing engine under-counts the Srinagar-Kupwara-Chowkibal hill road. Corridor real, near LoC. Lengthen Route_KM/cycle.</t>
+          <t>Uri via Baramulla on NH1 is ~100-102 km by road (distancesfrom 102 km) vs modelled 77.6 km - ~24% under. Engine likely under-routed the Baramulla-Uri mountain leg. Coords good. Corridor real, well-served to Baramulla, thinner Baramulla-Uri (border/army area). Fix: correct road km to ~100 km, refleet/headway.</t>
         </is>
       </c>
       <c r="K24" s="6" t="inlineStr">
         <is>
-          <t>distancesfrom.com srinagar-to-Chowkibal-Kupwara (125 km); alldistancebetween.com srinagar-chowkibal-kupwara</t>
+          <t>en.wikipedia.org/wiki/Srinagar-Baramulla_highway; distancesfrom.com srinagar-to-Uri (102 km); nativeplanet.com</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>SRKW02033906</t>
+          <t>SRGB01010903</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>Srinagar to Tangdar</t>
+          <t>Soura to Ganderbal</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>Regional_District</t>
+          <t>Urban</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>120.83</t>
+          <t>9.86</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H25" s="6" t="inlineStr">
@@ -2176,29 +2176,29 @@
       </c>
       <c r="I25" s="6" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
-          <t>Endpoint misplaced ~27 km short of actual Tangdhar (real town 34.40,73.86 across Sadhna Pass). Real road ~150-152 km vs modelled 121 km; engine under-models the 3000m Sadhna Pass switchbacks. 50-min headway is unrealistic for a border road truly served ~1-2 buses/day. Seasonality unmodelled (pass closes in winter).</t>
+          <t>Real driving distance for Soura/Srinagar to Ganderbal is commonly cited as 10-15 km depending on source and exact start point; modelled 9.86 km falls at the low end of that range, so it is plausible but on the short side. Treat as REVIEW for verification of the exact alignment used, not a hard error.</t>
         </is>
       </c>
       <c r="K25" s="6" t="inlineStr">
         <is>
-          <t>wanderon.in/blogs/teetwal-valley; mapsofindia.com/villages...karnah/tangdhar; kupwara.nic.in/tourist-place/sadhna</t>
+          <t>distancebetween2.com, onefivenine.com, ganderbal.nic.in</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>SRPW02033906</t>
+          <t>SRKW02013901</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>Srinagar to Ratnipora</t>
+          <t>Srinagar to Chowkibal</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
@@ -2208,22 +2208,22 @@
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>25.57</t>
+          <t>94.97</t>
         </is>
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>32.5</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="F26" s="6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H26" s="6" t="inlineStr">
@@ -2238,24 +2238,24 @@
       </c>
       <c r="J26" s="6" t="inlineStr">
         <is>
-          <t>Ratnipora is real (~5-6 km from Awantipora). Published distances route via Awantipora (~35-40 km); engine 25.6 km appears to take a more direct line and may UNDER-model the served corridor by ~29%. Confirm the route actually serves Awantipora/NH.</t>
+          <t>Chowkibal (Kupwara, on the Tangdhar/Sadhna Pass approach) real road ~125 km; engine 94.97 km under-models by ~25% - routing engine under-counts the Srinagar-Kupwara-Chowkibal hill road. Corridor real, near LoC. Lengthen Route_KM/cycle.</t>
         </is>
       </c>
       <c r="K26" s="6" t="inlineStr">
         <is>
-          <t>distancesfrom.com (Pulwama-Awantipora), distancebetween2.com (Srinagar-Awantipora), pulwama.gov.in</t>
+          <t>distancesfrom.com srinagar-to-Chowkibal-Kupwara (125 km); alldistancebetween.com srinagar-chowkibal-kupwara</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>SRPW02043902</t>
+          <t>SRKW02033906</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>Srinagar to Pasthoon</t>
+          <t>Srinagar to Tangdar</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
@@ -2263,24 +2263,24 @@
           <t>Regional_District</t>
         </is>
       </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="E27" s="7" t="inlineStr">
-        <is>
-          <t>41.5</t>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>120.83</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>151.0</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H27" s="6" t="inlineStr">
@@ -2295,106 +2295,106 @@
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>Pasthoon is a Tral-tehsil (Pulwama) village; coords correct district. Engine 50.0 km runs ~20% over a likely 38-45 km road via Awantipora (Tral itself is 40 km from Srinagar). KM over-modelled; verify routing.</t>
+          <t>Endpoint misplaced ~27 km short of actual Tangdhar (real town 34.40,73.86 across Sadhna Pass). Real road ~150-152 km vs modelled 121 km; engine under-models the 3000m Sadhna Pass switchbacks. 50-min headway is unrealistic for a border road truly served ~1-2 buses/day. Seasonality unmodelled (pass closes in winter).</t>
         </is>
       </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
-          <t>pulwama.gov.in, en.wikipedia.org/wiki/Tral, yatra.com</t>
+          <t>wanderon.in/blogs/teetwal-valley; mapsofindia.com/villages...karnah/tangdhar; kupwara.nic.in/tourist-place/sadhna</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>SRSR01010809</t>
+          <t>SRPW02033906</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>Rangpora to Soura</t>
+          <t>Srinagar to Ratnipora</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>Peri_Urban</t>
-        </is>
-      </c>
-      <c r="D28" s="7" t="inlineStr">
-        <is>
-          <t>22.05</t>
-        </is>
-      </c>
-      <c r="E28" s="7" t="inlineStr">
-        <is>
-          <t>4.0</t>
+          <t>Regional_District</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>25.57</t>
+        </is>
+      </c>
+      <c r="E28" s="8" t="inlineStr">
+        <is>
+          <t>32.5</t>
         </is>
       </c>
       <c r="F28" s="6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H28" s="6" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="I28" s="6" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J28" s="6" t="inlineStr">
         <is>
-          <t>Rangpora &amp; Soura adjacent (~3-5 km); engine 22 km is a mis-snap. Set to 4 km.</t>
+          <t>Ratnipora is real (~5-6 km from Awantipora). Published distances route via Awantipora (~35-40 km); engine 25.6 km appears to take a more direct line and may UNDER-model the served corridor by ~29%. Confirm the route actually serves Awantipora/NH.</t>
         </is>
       </c>
       <c r="K28" s="6" t="inlineStr">
         <is>
-          <t>Wikipedia Buchpora,Wikipedia Soura Srinagar,distancesfrom.com Lal Chowk-Soura via Nowhatta</t>
+          <t>distancesfrom.com (Pulwama-Awantipora), distancebetween2.com (Srinagar-Awantipora), pulwama.gov.in</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>SRSR01010904</t>
+          <t>SRPW02043902</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>Soura to Hazratbal</t>
+          <t>Srinagar to Pasthoon</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>Urban</t>
+          <t>Regional_District</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>8.34</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="F29" s="6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H29" s="6" t="inlineStr">
@@ -2404,59 +2404,59 @@
       </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
-          <t>Real road distance per alldistancebetween.com is about 6 km (7 min driving) vs modelled 8.337 km, a 39% overstatement, and the one-way time of ~33 min is roughly 3x the real drive time even allowing for stops. The corridor and headway/fleet are sound; the KM and cycle-time figures look inflated.</t>
+          <t>Pasthoon is a Tral-tehsil (Pulwama) village; coords correct district. Engine 50.0 km runs ~20% over a likely 38-45 km road via Awantipora (Tral itself is 40 km from Srinagar). KM over-modelled; verify routing.</t>
         </is>
       </c>
       <c r="K29" s="6" t="inlineStr">
         <is>
-          <t>alldistancebetween.com, onefivenine.com</t>
+          <t>pulwama.gov.in, en.wikipedia.org/wiki/Tral, yatra.com</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>SRSR01020422</t>
+          <t>SRSR01010809</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>Hazratbal to LD</t>
+          <t>Rangpora to Soura</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>Urban</t>
+          <t>Peri_Urban</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>9.29</t>
+          <t>22.05</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="F30" s="6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H30" s="6" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="I30" s="6" t="inlineStr">
@@ -2466,24 +2466,24 @@
       </c>
       <c r="J30" s="6" t="inlineStr">
         <is>
-          <t>Distance premium (haversine 5.76 vs modelled 9.3 km, +61%) is higher than typical for a direct Hazratbal-LD hop; either an unstated via-detour exists or the route geometry needs rechecking. Corridor and both endpoints are real and served.</t>
+          <t>Rangpora &amp; Soura adjacent (~3-5 km); engine 22 km is a mis-snap. Set to 4 km.</t>
         </is>
       </c>
       <c r="K30" s="6" t="inlineStr">
         <is>
-          <t>wikipedia.org (Hazratbal),onefivenine.com,kashmirlife.net</t>
+          <t>Wikipedia Buchpora,Wikipedia Soura Srinagar,distancesfrom.com Lal Chowk-Soura via Nowhatta</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>SRSR01020522</t>
+          <t>SRSR01010904</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>Lalbazar to LD</t>
+          <t>Soura to Hazratbal</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
@@ -2493,22 +2493,22 @@
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>9.31</t>
+          <t>8.34</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="F31" s="6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H31" s="6" t="inlineStr">
@@ -2518,29 +2518,29 @@
       </c>
       <c r="I31" s="6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
-          <t>KM_Delta is large in percentage terms but the absolute gap is only ~2-3 km, typical for very short urban routes; cycle time and headway look generous - worth re-checking origin pin for Lal Bazar</t>
+          <t>Real road distance per alldistancebetween.com is about 6 km (7 min driving) vs modelled 8.337 km, a 39% overstatement, and the one-way time of ~33 min is roughly 3x the real drive time even allowing for stops. The corridor and headway/fleet are sound; the KM and cycle-time figures look inflated.</t>
         </is>
       </c>
       <c r="K31" s="6" t="inlineStr">
         <is>
-          <t>onefivenine.com, distancesfrom.com, wikipedia.org</t>
+          <t>alldistancebetween.com, onefivenine.com</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>SRSR01020529</t>
+          <t>SRSR01020422</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>Lalbazar to Parimpora</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
@@ -2550,12 +2550,12 @@
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>12.65</t>
+          <t>9.29</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="F32" s="6" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="G32" s="6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H32" s="6" t="inlineStr">
@@ -2580,24 +2580,24 @@
       </c>
       <c r="J32" s="6" t="inlineStr">
         <is>
-          <t>Distance and corridor are plausible but on the upper edge of tolerance; cycle time is generous - flag for headway/fleet re-check rather than route validity</t>
+          <t>Distance premium (haversine 5.76 vs modelled 9.3 km, +61%) is higher than typical for a direct Hazratbal-LD hop; either an unstated via-detour exists or the route geometry needs rechecking. Corridor and both endpoints are real and served.</t>
         </is>
       </c>
       <c r="K32" s="6" t="inlineStr">
         <is>
-          <t>onefivenine.com, indiamapia.com</t>
+          <t>wikipedia.org (Hazratbal),onefivenine.com,kashmirlife.net</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>SRSR01020622</t>
+          <t>SRSR01020522</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>Malbagh to LD</t>
+          <t>Lalbazar to LD</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
@@ -2607,22 +2607,22 @@
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>11.43</t>
+          <t>9.31</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H33" s="6" t="inlineStr">
@@ -2637,49 +2637,49 @@
       </c>
       <c r="J33" s="6" t="inlineStr">
         <is>
-          <t>Real corridor and coordinates check out; modelled cycle time runs a bit long relative to the short distance - fleet of 6 for a 20 min headway, 0.165 load looks generous but not unreasonable for a hospital-bound route</t>
+          <t>KM_Delta is large in percentage terms but the absolute gap is only ~2-3 km, typical for very short urban routes; cycle time and headway look generous - worth re-checking origin pin for Lal Bazar</t>
         </is>
       </c>
       <c r="K33" s="6" t="inlineStr">
         <is>
-          <t>onefivenine.com (Malabagh locality), srinagar.nic.in (LD Hospital)</t>
+          <t>onefivenine.com, distancesfrom.com, wikipedia.org</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>SRSR01020822</t>
+          <t>SRSR01020529</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>Rangpora to LD</t>
+          <t>Lalbazar to Parimpora</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>Peri_Urban</t>
+          <t>Urban</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>21.92</t>
+          <t>12.65</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G34" s="6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H34" s="6" t="inlineStr">
@@ -2694,24 +2694,24 @@
       </c>
       <c r="J34" s="6" t="inlineStr">
         <is>
-          <t>Engine's Rangpora-to-LD distance (21.9 km) is far above the ~9-11 km a direct Ganderbal-road-to-Karan Nagar run would imply (haversine only 8.93 km); this is the largest circuity outlier in the batch and likely reflects either a coordinate snap error or an unrealistic routed path -- recommend re-running OSRM for this O-D pair specifically.</t>
+          <t>Distance and corridor are plausible but on the upper edge of tolerance; cycle time is generous - flag for headway/fleet re-check rather than route validity</t>
         </is>
       </c>
       <c r="K34" s="6" t="inlineStr">
         <is>
-          <t>Wikipedia Buchpora,srinagar.nic.in Lal Ded Hospital,mappls.com Lalla Ded Hospital</t>
+          <t>onefivenine.com, indiamapia.com</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>SRSR01020913</t>
+          <t>SRSR01020622</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>Soura to Dalgate</t>
+          <t>Malbagh to LD</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
@@ -2721,12 +2721,12 @@
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>11.74</t>
+          <t>11.43</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="F35" s="6" t="inlineStr">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G35" s="6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H35" s="6" t="inlineStr">
@@ -2751,49 +2751,49 @@
       </c>
       <c r="J35" s="6" t="inlineStr">
         <is>
-          <t>Real road distance (~7 km via distancesfrom.com) is well below the modelled 11.745 km, a 68% overstatement; likely the engine routed via a longer corridor than the direct Soura-Dalgate Bridge road. Headway 20 min and fleet 6 are still plausible for an urban link given the high cycle time used.</t>
+          <t>Real corridor and coordinates check out; modelled cycle time runs a bit long relative to the short distance - fleet of 6 for a 20 min headway, 0.165 load looks generous but not unreasonable for a hospital-bound route</t>
         </is>
       </c>
       <c r="K35" s="6" t="inlineStr">
         <is>
-          <t>distancesfrom.com, Wikipedia Soura</t>
+          <t>onefivenine.com (Malabagh locality), srinagar.nic.in (LD Hospital)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>SRSR02011109</t>
+          <t>SRSR01020822</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>Chanapora to Soura</t>
+          <t>Rangpora to LD</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>Urban</t>
+          <t>Peri_Urban</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>14.11</t>
+          <t>21.92</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="F36" s="6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G36" s="6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H36" s="6" t="inlineStr">
@@ -2803,56 +2803,56 @@
       </c>
       <c r="I36" s="6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J36" s="6" t="inlineStr">
         <is>
-          <t>KM delta is within tolerance but the implied average speed (~16 km/h one-way) is slow even for Srinagar city traffic; verify whether the route truly transits downtown or has a more direct alignment via the bypass.</t>
+          <t>Engine's Rangpora-to-LD distance (21.9 km) is far above the ~9-11 km a direct Ganderbal-road-to-Karan Nagar run would imply (haversine only 8.93 km); this is the largest circuity outlier in the batch and likely reflects either a coordinate snap error or an unrealistic routed path -- recommend re-running OSRM for this O-D pair specifically.</t>
         </is>
       </c>
       <c r="K36" s="6" t="inlineStr">
         <is>
-          <t>wikipedia.org (Soura, Srinagar),onefivenine.com,alldistancebetween.com</t>
+          <t>Wikipedia Buchpora,srinagar.nic.in Lal Ded Hospital,mappls.com Lalla Ded Hospital</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>SRSR02012904</t>
+          <t>SRSR01020913</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>Parimpora to Hazratbal</t>
+          <t>Soura to Dalgate</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>Peri_Urban</t>
+          <t>Urban</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>16.1</t>
+          <t>11.74</t>
         </is>
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="F37" s="6" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G37" s="6" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G37" s="6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="H37" s="6" t="inlineStr">
         <is>
           <t>AUTO</t>
@@ -2860,29 +2860,29 @@
       </c>
       <c r="I37" s="6" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J37" s="6" t="inlineStr">
         <is>
-          <t>Corridor is real and even independently corroborated as an existing SSCL route ('Route 9 from Parimpora to Hazratbal' in a published 16-route list), but this specific engine row is marked CMP_Trunk=False despite SSCL apparently operating exactly this corridor, and the modelled 16.1km/80.5min cycle is on the high side versus the ~9-12km/15-18min one-way that direct-route sources suggest, even allowing for the lakeside detour.</t>
+          <t>Real road distance (~7 km via distancesfrom.com) is well below the modelled 11.745 km, a 68% overstatement; likely the engine routed via a longer corridor than the direct Soura-Dalgate Bridge road. Headway 20 min and fleet 6 are still plausible for an urban link given the high cycle time used.</t>
         </is>
       </c>
       <c r="K37" s="6" t="inlineStr">
         <is>
-          <t>kashmirlife.net, wikipedia.org</t>
+          <t>distancesfrom.com, Wikipedia Soura</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>SRSR02013004</t>
+          <t>SRSR02011109</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>Qamarwari to Hazratbal</t>
+          <t>Chanapora to Soura</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
@@ -2892,22 +2892,22 @@
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>14.08</t>
+          <t>14.11</t>
         </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>11.5</t>
         </is>
       </c>
       <c r="F38" s="6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G38" s="6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H38" s="6" t="inlineStr">
@@ -2917,44 +2917,44 @@
       </c>
       <c r="I38" s="6" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J38" s="6" t="inlineStr">
         <is>
-          <t>Web sources independently confirm Qamarwari-Hazratbal is ~7 km/~12-20 min by road, but engine models 14.08 km and a ~55-min one-way time — roughly double; likely an indirect/looped path or unit issue in the engine route geometry.</t>
+          <t>KM delta is within tolerance but the implied average speed (~16 km/h one-way) is slow even for Srinagar city traffic; verify whether the route truly transits downtown or has a more direct alignment via the bypass.</t>
         </is>
       </c>
       <c r="K38" s="6" t="inlineStr">
         <is>
-          <t>alldistancebetween.com,distancesfrom.com,waze.com</t>
+          <t>wikipedia.org (Soura, Srinagar),onefivenine.com,alldistancebetween.com</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>SRSR02020223</t>
+          <t>SRSR02012904</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>Baghat Shora to Lalchowk</t>
+          <t>Parimpora to Hazratbal</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>Urban</t>
+          <t>Peri_Urban</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>16.1</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="F39" s="6" t="inlineStr">
@@ -2979,24 +2979,24 @@
       </c>
       <c r="J39" s="6" t="inlineStr">
         <is>
-          <t>Baghat (Shora) is documented as only 2-7 km from Lal Chowk by multiple sources (Barzulla ~2km, Bagh-e-Mehtab ~7km), but the engine models a 13 km, 52-minute one-way route for this short intra-city hop -- the routing/coordinate likely picked up a circuitous OSRM path or a less-central 'Shora' sub-point; recommend verifying the exact Baghat Shora coordinate and routing.</t>
+          <t>Corridor is real and even independently corroborated as an existing SSCL route ('Route 9 from Parimpora to Hazratbal' in a published 16-route list), but this specific engine row is marked CMP_Trunk=False despite SSCL apparently operating exactly this corridor, and the modelled 16.1km/80.5min cycle is on the high side versus the ~9-12km/15-18min one-way that direct-route sources suggest, even allowing for the lakeside detour.</t>
         </is>
       </c>
       <c r="K39" s="6" t="inlineStr">
         <is>
-          <t>onefivenine.com (Baghat locality), distancesfrom.com, latlong.net (Lal Chowk)</t>
+          <t>kashmirlife.net, wikipedia.org</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>SRSR02020613</t>
+          <t>SRSR02013004</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>Batmaloo to Dalgate</t>
+          <t>Qamarwari to Hazratbal</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
@@ -3006,17 +3006,17 @@
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>14.08</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="F40" s="6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G40" s="6" t="inlineStr">
@@ -3031,29 +3031,29 @@
       </c>
       <c r="I40" s="6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J40" s="6" t="inlineStr">
         <is>
-          <t>Modelled road distance (5.4 km) is roughly 80% longer than straight-line (3.0 km); within tolerance for a short urban route given the documented Dalgate one-way detours, but extremely low load (0.008) suggests this route may be redundant with other Batamaloo-area services — flag for de-duplication.</t>
+          <t>Web sources independently confirm Qamarwari-Hazratbal is ~7 km/~12-20 min by road, but engine models 14.08 km and a ~55-min one-way time — roughly double; likely an indirect/looped path or unit issue in the engine route geometry.</t>
         </is>
       </c>
       <c r="K40" s="6" t="inlineStr">
         <is>
-          <t>onefivenine.com,distcalculator.com,tribuneindia.com</t>
+          <t>alldistancebetween.com,distancesfrom.com,waze.com</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>SRSR02021807</t>
+          <t>SRSR02020223</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>JVC to Batwara</t>
+          <t>Baghat Shora to Lalchowk</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
@@ -3063,22 +3063,22 @@
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>14.66</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="F41" s="6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H41" s="6" t="inlineStr">
@@ -3093,24 +3093,24 @@
       </c>
       <c r="J41" s="6" t="inlineStr">
         <is>
-          <t>KM premium (+66% over haversine) and slow implied speed (~15 km/h one-way) are both on the high end; corridor and endpoints (JVC Hospital Bemina; Batwara) are real, but the routing/cycle-time should be rechecked against an actual road path.</t>
+          <t>Baghat (Shora) is documented as only 2-7 km from Lal Chowk by multiple sources (Barzulla ~2km, Bagh-e-Mehtab ~7km), but the engine models a 13 km, 52-minute one-way route for this short intra-city hop -- the routing/coordinate likely picked up a circuitous OSRM path or a less-central 'Shora' sub-point; recommend verifying the exact Baghat Shora coordinate and routing.</t>
         </is>
       </c>
       <c r="K41" s="6" t="inlineStr">
         <is>
-          <t>mappls.com (JVC Hospital Bemina),justdial.com,onefivenine.com (Jawahar Nagar)</t>
+          <t>onefivenine.com (Baghat locality), distancesfrom.com, latlong.net (Lal Chowk)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>SRSR02022018</t>
+          <t>SRSR02020613</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>Jehangir Chowk to JVC</t>
+          <t>Batmaloo to Dalgate</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
@@ -3120,24 +3120,24 @@
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>5.37</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="F42" s="6" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G42" s="6" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G42" s="6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="H42" s="6" t="inlineStr">
         <is>
           <t>AUTO</t>
@@ -3145,56 +3145,56 @@
       </c>
       <c r="I42" s="6" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J42" s="6" t="inlineStr">
         <is>
-          <t>KM premium is high (+54% to +93% over haversine) for a sub-8 km urban route; while within the wider ±25% short-route tolerance band only at the low end of the range, this and the related JVC-to-Batwara route both show elevated circuity — worth a routing recheck.</t>
+          <t>Modelled road distance (5.4 km) is roughly 80% longer than straight-line (3.0 km); within tolerance for a short urban route given the documented Dalgate one-way detours, but extremely low load (0.008) suggests this route may be redundant with other Batamaloo-area services — flag for de-duplication.</t>
         </is>
       </c>
       <c r="K42" s="6" t="inlineStr">
         <is>
-          <t>mappls.com (JVC Hospital Bemina),justdial.com</t>
+          <t>onefivenine.com,distcalculator.com,tribuneindia.com</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>SRSR02022028</t>
+          <t>SRSR02021807</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>Jehangir Chowk to Panzinara</t>
+          <t>JVC to Batwara</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>Peri_Urban</t>
+          <t>Urban</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>16.49</t>
+          <t>14.66</t>
         </is>
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="F43" s="6" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G43" s="6" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G43" s="6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="H43" s="6" t="inlineStr">
         <is>
           <t>AUTO</t>
@@ -3207,24 +3207,24 @@
       </c>
       <c r="J43" s="6" t="inlineStr">
         <is>
-          <t>There is a real in-city Panzinara locality in Srinagar (near Qamarwari/Parimpora, documented by onefivenine.com and jkpanchayat.jk.gov.in) only a few km from Jehangir Chowk, but the engine's destination coordinate sits roughly 13-16km further out, closer to the Budgam district boundary. This is either a legitimate but different, further-out Panzinara, or a geocoding mismatch between two same-named places; resolving which Panzinara was intended is needed before the 16.5km/82.5min figures can be confirmed.</t>
+          <t>KM premium (+66% over haversine) and slow implied speed (~15 km/h one-way) are both on the high end; corridor and endpoints (JVC Hospital Bemina; Batwara) are real, but the routing/cycle-time should be rechecked against an actual road path.</t>
         </is>
       </c>
       <c r="K43" s="6" t="inlineStr">
         <is>
-          <t>onefivenine.com,jkpanchayat.jk.gov.in,mapsofindia.com</t>
+          <t>mappls.com (JVC Hospital Bemina),justdial.com,onefivenine.com (Jawahar Nagar)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>SRSR02022229</t>
+          <t>SRSR02022018</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>LD to Parimpora</t>
+          <t>Jehangir Chowk to JVC</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
@@ -3234,17 +3234,17 @@
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>10.44</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="F44" s="6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G44" s="6" t="inlineStr">
@@ -3264,49 +3264,49 @@
       </c>
       <c r="J44" s="6" t="inlineStr">
         <is>
-          <t>Modelled one-way time appears generous relative to the short distance; otherwise corridor and coordinates check out fine</t>
+          <t>KM premium is high (+54% to +93% over haversine) for a sub-8 km urban route; while within the wider ±25% short-route tolerance band only at the low end of the range, this and the related JVC-to-Batwara route both show elevated circuity — worth a routing recheck.</t>
         </is>
       </c>
       <c r="K44" s="6" t="inlineStr">
         <is>
-          <t>onefivenine.com, indiamapia.com, jksrtc.co.in</t>
+          <t>mappls.com (JVC Hospital Bemina),justdial.com</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>SRSR02022938</t>
+          <t>SRSR02022028</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>Parimpora to Saidakadal</t>
+          <t>Jehangir Chowk to Panzinara</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>Urban</t>
+          <t>Peri_Urban</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>14.07</t>
+          <t>16.49</t>
         </is>
       </c>
       <c r="E45" s="7" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="F45" s="6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G45" s="6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H45" s="6" t="inlineStr">
@@ -3316,29 +3316,29 @@
       </c>
       <c r="I45" s="6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J45" s="6" t="inlineStr">
         <is>
-          <t>Engine KM (14.07) is roughly 41-56% higher than a realistic 8-10 km road distance between Parimpora and old-city Saidakadal; likely an inflated/indirect engine path. Corridor itself and headway/fleet are otherwise plausible given old-city congestion.</t>
+          <t>There is a real in-city Panzinara locality in Srinagar (near Qamarwari/Parimpora, documented by onefivenine.com and jkpanchayat.jk.gov.in) only a few km from Jehangir Chowk, but the engine's destination coordinate sits roughly 13-16km further out, closer to the Budgam district boundary. This is either a legitimate but different, further-out Panzinara, or a geocoding mismatch between two same-named places; resolving which Panzinara was intended is needed before the 16.5km/82.5min figures can be confirmed.</t>
         </is>
       </c>
       <c r="K45" s="6" t="inlineStr">
         <is>
-          <t>kashmirlife.net,mapcarta.com,onefivenine.com</t>
+          <t>onefivenine.com,jkpanchayat.jk.gov.in,mapsofindia.com</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>SRSR02022941</t>
+          <t>SRSR02022229</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>Hazratbal, Lalbazar</t>
+          <t>LD to Parimpora</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
@@ -3348,12 +3348,12 @@
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>8.81</t>
+          <t>10.44</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="F46" s="6" t="inlineStr">
@@ -3378,24 +3378,24 @@
       </c>
       <c r="J46" s="6" t="inlineStr">
         <is>
-          <t>Route name says 'Hazratbal' but O coordinate (34.111187,74.747451) matches Parimpora, not the true Hazratbal point used elsewhere (34.127549,74.835646) — likely a naming/endpoint mismatch from route consolidation; verify intended origin.</t>
+          <t>Modelled one-way time appears generous relative to the short distance; otherwise corridor and coordinates check out fine</t>
         </is>
       </c>
       <c r="K46" s="6" t="inlineStr">
         <is>
-          <t>onefivenine.com (Lal Bazar); wikipedia.org (Hazratbal); indiainfo.net</t>
+          <t>onefivenine.com, indiamapia.com, jksrtc.co.in</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>SRSR02023020</t>
+          <t>SRSR02022938</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>Qamarwari to Jehangir Chowk</t>
+          <t>Parimpora to Saidakadal</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
@@ -3405,22 +3405,22 @@
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>12.66</t>
+          <t>14.07</t>
         </is>
       </c>
       <c r="E47" s="7" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="F47" s="6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G47" s="6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H47" s="6" t="inlineStr">
@@ -3430,29 +3430,29 @@
       </c>
       <c r="I47" s="6" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J47" s="6" t="inlineStr">
         <is>
-          <t>Engine KM (12.66) is more than double the haversine (4.38 km) and well above any reasonable road-detour factor for two adjacent central-Srinagar points; route geometry likely includes an unnecessary loop. Corridor and headway/fleet otherwise sane.</t>
+          <t>Engine KM (14.07) is roughly 41-56% higher than a realistic 8-10 km road distance between Parimpora and old-city Saidakadal; likely an inflated/indirect engine path. Corridor itself and headway/fleet are otherwise plausible given old-city congestion.</t>
         </is>
       </c>
       <c r="K47" s="6" t="inlineStr">
         <is>
-          <t>tellmyroute.com,kashmirlife.net,onefivenine.com</t>
+          <t>kashmirlife.net,mapcarta.com,onefivenine.com</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>SRSR02023029</t>
+          <t>SRSR02023020</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>Qamarwari to Parimpora</t>
+          <t>Qamarwari to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
@@ -3462,22 +3462,22 @@
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>14.58</t>
+          <t>12.66</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="F48" s="6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G48" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H48" s="6" t="inlineStr">
@@ -3492,67 +3492,124 @@
       </c>
       <c r="J48" s="6" t="inlineStr">
         <is>
-          <t>Severe distance mismatch: independently-confirmed adjacency (~0.8-3 km, both on JKRTC Route 9) versus engine's 14.58 km / ~55-min one-way; engine geometry for this pair is almost certainly wrong (likely picked up a long detour or mis-snapped node).</t>
+          <t>Engine KM (12.66) is more than double the haversine (4.38 km) and well above any reasonable road-detour factor for two adjacent central-Srinagar points; route geometry likely includes an unnecessary loop. Corridor and headway/fleet otherwise sane.</t>
         </is>
       </c>
       <c r="K48" s="6" t="inlineStr">
         <is>
-          <t>mappls.com,kashmirlife.net,onefivenine.com</t>
+          <t>tellmyroute.com,kashmirlife.net,onefivenine.com</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
+          <t>SRSR02023029</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>Qamarwari to Parimpora</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t>14.58</t>
+        </is>
+      </c>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="F49" s="6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G49" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H49" s="6" t="inlineStr">
+        <is>
+          <t>AUTO</t>
+        </is>
+      </c>
+      <c r="I49" s="6" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J49" s="6" t="inlineStr">
+        <is>
+          <t>Severe distance mismatch: independently-confirmed adjacency (~0.8-3 km, both on JKRTC Route 9) versus engine's 14.58 km / ~55-min one-way; engine geometry for this pair is almost certainly wrong (likely picked up a long detour or mis-snapped node).</t>
+        </is>
+      </c>
+      <c r="K49" s="6" t="inlineStr">
+        <is>
+          <t>mappls.com,kashmirlife.net,onefivenine.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
           <t>SRSR02023810</t>
         </is>
       </c>
-      <c r="B49" s="6" t="inlineStr">
+      <c r="B50" s="6" t="inlineStr">
         <is>
           <t>Saidakadal to Bypass</t>
         </is>
       </c>
-      <c r="C49" s="6" t="inlineStr">
+      <c r="C50" s="6" t="inlineStr">
         <is>
           <t>Urban</t>
         </is>
       </c>
-      <c r="D49" s="7" t="inlineStr">
+      <c r="D50" s="7" t="inlineStr">
         <is>
           <t>13.28</t>
         </is>
       </c>
-      <c r="E49" s="7" t="inlineStr">
+      <c r="E50" s="7" t="inlineStr">
         <is>
           <t>7.5</t>
         </is>
       </c>
-      <c r="F49" s="6" t="inlineStr">
+      <c r="F50" s="6" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="G49" s="6" t="inlineStr">
+      <c r="G50" s="6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="H49" s="6" t="inlineStr">
+      <c r="H50" s="6" t="inlineStr">
         <is>
           <t>AUTO</t>
         </is>
       </c>
-      <c r="I49" s="6" t="inlineStr">
+      <c r="I50" s="6" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="J49" s="6" t="inlineStr">
+      <c r="J50" s="6" t="inlineStr">
         <is>
           <t>Engine KM (13.28) is roughly double the haversine (6.33 km) and the implied detour factor (~2.1x) is high even for Srinagar's old-city street grid; corridor existence (old city to bypass) is plausible but the specific routed distance looks inflated.</t>
         </is>
       </c>
-      <c r="K49" s="6" t="inlineStr">
+      <c r="K50" s="6" t="inlineStr">
         <is>
           <t>greaterkashmir.com,mapcarta.com,kashmirobserver.net</t>
         </is>
@@ -3569,7 +3626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C46"/>
+  <dimension ref="A1:C45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4311,12 +4368,12 @@
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>SRGB02020503</t>
+          <t>SRSR02022728</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>Batamaloo to Manigam</t>
+          <t>Pantha Chowk to Panzinara</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
@@ -4328,32 +4385,15 @@
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>SRSR02022728</t>
+          <t>SRBG02060502</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>Pantha Chowk to Panzinara</t>
+          <t>Batamaloo to Dc Office Budgam</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
-        <is>
-          <t>SSCL trunk — legit via-loop, not corrected</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="6" t="inlineStr">
-        <is>
-          <t>SRBG02060502</t>
-        </is>
-      </c>
-      <c r="B46" s="6" t="inlineStr">
-        <is>
-          <t>Batamaloo to Dc Office Budgam</t>
-        </is>
-      </c>
-      <c r="C46" s="6" t="inlineStr">
         <is>
           <t>SSCL trunk — legit via-loop, not corrected</t>
         </is>
